--- a/PCB/Plan de test/PDT_Trotinette_JR_AM.xlsx
+++ b/PCB/Plan de test/PDT_Trotinette_JR_AM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AraGr\OneDrive\Bureau\Cegep\Cegep Session 4\Projet integrateur 2\Projet trotinette\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AraGr\OneDrive\Bureau\Cegep\Cegep Session 4\Projet integrateur 2\Projet trotinette\Projet-integrateur\PCB\Plan de test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA7438A-F45A-4340-BC3F-22DC4ABA9910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B71A08-56D1-4ECD-91FE-7CFA90B23956}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CF7E7B00-0B90-4AA1-96DC-F02D56B415EB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CF7E7B00-0B90-4AA1-96DC-F02D56B415EB}"/>
   </bookViews>
   <sheets>
     <sheet name="Tests" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="72">
   <si>
     <t>Plan de tests</t>
   </si>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t>Mettre un jumper sur le bornier J3 entre la broche du milieu et l'indicateur ALIM_USB puis, brancher la carte et mesurer la tension entre les points USB / 5V / 3V3 et l'extérieur du connecteur USB.  (La valeur du point de test USB devrait etre d'environ 5V et le 3V3 devrait se situer entre 3.2 et 3.4V)</t>
-  </si>
-  <si>
-    <t>Tableau de bord trotinette</t>
   </si>
   <si>
     <t>Projet intégrateur 2</t>
@@ -227,6 +224,38 @@
   </si>
   <si>
     <t>Le connecteur passe bien et n'accroche pas</t>
+  </si>
+  <si>
+    <t>Il est possible d'alimenter le circuit par l'alimentation du rasberry Pi avec une tension de 3.29V sur le point de test 3V3 et 4.95V sur le point de test 5V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le PCB n'est jamais détecté par l'interface </t>
+  </si>
+  <si>
+    <t>Activation des options flash dans CUBEMX afin de permettre le controle du mode BOOT avec la broche BOOT0</t>
+  </si>
+  <si>
+    <t>L'option NOE du debug USB ne peut être activé en même temps que SWD ce qui bloque la communication.</t>
+  </si>
+  <si>
+    <t>Il est possible de visionner les informations mais très bruité à cause du cable.
+À retester mais souder directement sur les broches pour bypasser le fil.</t>
+  </si>
+  <si>
+    <t>L'interface CUBEIDE arrive à se connecter au circuit et à transmettre le code dans le PCB</t>
+  </si>
+  <si>
+    <t>Fonctionalité non testable par manque de temps lors de la programmation.</t>
+  </si>
+  <si>
+    <t>Soudure de fils directement sur les broches du connecteur pour eviter le bruit du cable fournit par enseignant.</t>
+  </si>
+  <si>
+    <t>Le code bloquant empêche la bonne lecture du message recu par l'interface UART2 vers UART1
+***Il faudrait faire une nouvelle version avec un code utilisant des interrupts***</t>
+  </si>
+  <si>
+    <t>Tableau de bord trottinette</t>
   </si>
 </sst>
 </file>
@@ -453,7 +482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -517,11 +546,58 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -853,26 +929,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}" name="Table3" displayName="Table3" ref="B10:H33" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}" name="Table3" displayName="Table3" ref="B10:H33" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19">
   <autoFilter ref="B10:H33" xr:uid="{3E4F9C66-3C4F-4FED-86C7-317DD6AF871B}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{21BD1CA3-33DE-44AA-9EB4-FC84914AA01E}" name="Fonction" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{40F1DB91-EE19-4388-9FD9-FC665131A01C}" name="Description du test" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{46119054-E687-474D-A236-70842A202FA2}" name="Résultat" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{E76DCA99-A14D-4F97-96AC-0659630D86A5}" name="Raison réussite ou échec" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{C0DEE3AC-0260-44EA-839D-A616D9FF1BF7}" name="modification effectuée" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{EB8F3DD3-BA06-4471-97FB-7FC066A8F5DD}" name="Nouveau résultat" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{853C2233-5CDD-4625-B476-83FD3F9762B1}" name="Commentaire" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{21BD1CA3-33DE-44AA-9EB4-FC84914AA01E}" name="Fonction" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{40F1DB91-EE19-4388-9FD9-FC665131A01C}" name="Description du test" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{46119054-E687-474D-A236-70842A202FA2}" name="Résultat" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{E76DCA99-A14D-4F97-96AC-0659630D86A5}" name="Raison réussite ou échec" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{C0DEE3AC-0260-44EA-839D-A616D9FF1BF7}" name="modification effectuée" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{EB8F3DD3-BA06-4471-97FB-7FC066A8F5DD}" name="Nouveau résultat" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{853C2233-5CDD-4625-B476-83FD3F9762B1}" name="Commentaire" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6C077BD4-392F-43DD-BBA4-D8EFAD3C2DF3}" name="Table38" displayName="Table38" ref="B2:E15" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" dataCellStyle="Normal">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6C077BD4-392F-43DD-BBA4-D8EFAD3C2DF3}" name="Table38" displayName="Table38" ref="B2:E15" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" dataCellStyle="Normal">
   <autoFilter ref="B2:E15" xr:uid="{6C077BD4-392F-43DD-BBA4-D8EFAD3C2DF3}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D8886178-DA38-4DAF-A779-65758840ADDA}" name="#" dataDxfId="4" dataCellStyle="Normal">
+    <tableColumn id="1" xr3:uid="{D8886178-DA38-4DAF-A779-65758840ADDA}" name="#" dataDxfId="8" dataCellStyle="Normal">
       <calculatedColumnFormula>B2+1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{F83C734D-9C3E-4041-9C4C-0512ABCBDEB0}" name="Modification suggérée" dataCellStyle="Normal"/>
@@ -884,9 +960,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -924,7 +1000,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1030,7 +1106,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1172,7 +1248,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1223,13 +1299,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
@@ -1240,12 +1316,14 @@
         <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="6"/>
+      <c r="E6" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
@@ -1257,7 +1335,9 @@
       <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="6"/>
+      <c r="E7" s="29">
+        <v>46117</v>
+      </c>
     </row>
     <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="7" t="s">
@@ -1315,7 +1395,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
@@ -1326,13 +1406,13 @@
         <v>11</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
@@ -1343,13 +1423,13 @@
         <v>11</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D13" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13" s="18"/>
       <c r="G13" s="18"/>
@@ -1366,7 +1446,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" s="18"/>
       <c r="G14" s="18"/>
@@ -1383,7 +1463,7 @@
         <v>1</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15" s="18"/>
       <c r="G15" s="18"/>
@@ -1400,7 +1480,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F16" s="18"/>
       <c r="G16" s="18"/>
@@ -1417,7 +1497,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18"/>
@@ -1434,16 +1514,16 @@
         <v>4</v>
       </c>
       <c r="E18" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="18" t="s">
+      <c r="G18" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="H18" s="18" t="s">
         <v>60</v>
-      </c>
-      <c r="G18" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="63" customHeight="1" x14ac:dyDescent="0.3">
@@ -1457,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
@@ -1474,7 +1554,7 @@
         <v>1</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
@@ -1491,7 +1571,7 @@
         <v>1</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
@@ -1508,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
@@ -1519,10 +1599,14 @@
         <v>20</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="18"/>
+        <v>36</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>62</v>
+      </c>
       <c r="F23" s="18"/>
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
@@ -1532,51 +1616,75 @@
         <v>20</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E24" s="18"/>
+      <c r="E24" s="18" t="s">
+        <v>67</v>
+      </c>
       <c r="F24" s="18"/>
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
     </row>
-    <row r="25" spans="2:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:8" ht="95.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="16"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-    </row>
-    <row r="26" spans="2:8" ht="21" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G25" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="16"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
+        <v>43</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="18" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="27" spans="2:8" ht="21" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="16"/>
-      <c r="E27" s="18"/>
+      <c r="E27" s="18" t="s">
+        <v>68</v>
+      </c>
       <c r="F27" s="18"/>
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
@@ -1631,7 +1739,7 @@
       <c r="C33" s="15"/>
       <c r="D33" s="25"/>
       <c r="E33" s="18" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F33" s="18"/>
       <c r="G33" s="18"/>
@@ -1716,26 +1824,44 @@
     <mergeCell ref="C2:C4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D11:D33 G11:G33">
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="Échec">
+  <conditionalFormatting sqref="D11:D24 G11:G24 G27:G33 D27:D33">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="Échec">
       <formula>NOT(ISERROR(SEARCH("Échec",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11:H33">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="F11:H24 F27:H33">
+    <cfRule type="expression" dxfId="6" priority="5">
       <formula>$D11=""</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>$D11="Réussi"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G33 D11:D33">
-    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Réussi">
+  <conditionalFormatting sqref="G11:G24 D11:D24 D27:D33 G27:G33">
+    <cfRule type="containsText" dxfId="4" priority="7" operator="containsText" text="Réussi">
       <formula>NOT(ISERROR(SEARCH("Réussi",D11)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D25:D26 G25:G26">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Échec">
+      <formula>NOT(ISERROR(SEARCH("Échec",D25)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F25:H26">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>$D25=""</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$D25="Réussi"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25:G26 D25:D26">
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="Réussi">
+      <formula>NOT(ISERROR(SEARCH("Réussi",D25)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D33 G11:G33" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G33 D11:D33" xr:uid="{FE4B82E2-1996-4D3C-82E2-B8CCB3918355}">
       <formula1>$J$4:$J$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:B33" xr:uid="{78441C5B-4219-4854-877A-7D3169F5D56F}">
@@ -1780,7 +1906,7 @@
         <v>23</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -1791,11 +1917,11 @@
         <v>1</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="22"/>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
@@ -1970,6 +2096,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100579959CCCCA5C544BBD30F9226CE8516" ma:contentTypeVersion="4" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="18a3a6cb6fca627387261b481e951241">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88fb2577-ad7a-4d43-8167-cef18aea1aa3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c32280d31556b1ec6db52af4e194afa7" ns2:_="">
     <xsd:import namespace="88fb2577-ad7a-4d43-8167-cef18aea1aa3"/>
@@ -2113,7 +2245,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2122,13 +2254,16 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BFFA3822-A47A-4455-B0B9-162E8DE8BA4F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2146,19 +2281,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBF659F0-93B9-47A9-A708-8A09E9128827}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56D71B08-E827-483B-9150-DAAFA24A9B1C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>